--- a/tests/systeem_testen/224/results/df_beta_vakken.xlsx
+++ b/tests/systeem_testen/224/results/df_beta_vakken.xlsx
@@ -452,53 +452,53 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>9.839010769011201</v>
+        <v>14.27481990390891</v>
       </c>
       <c r="E2" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.570490951438946e-46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.839010769011201</v>
+        <v>13.91953628013584</v>
       </c>
       <c r="E3" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.410106294400354e-44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>9.839010769011201</v>
+        <v>13.282481226944</v>
       </c>
       <c r="E4" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.46268743978562e-40</v>
       </c>
     </row>
     <row r="5">
@@ -512,44 +512,44 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>9.839010769011201</v>
+        <v>13.36019126533477</v>
       </c>
       <c r="E5" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.164919137477e-41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>9.839010769011201</v>
+        <v>13.39041489308758</v>
       </c>
       <c r="E6" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.439768555147069e-41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9.839010769011201</v>
+        <v>13.45281484550868</v>
       </c>
       <c r="E7" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.481858553203805e-41</v>
       </c>
     </row>
   </sheetData>
